--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -33,6 +33,9 @@
   </si>
   <si>
     <t xml:space="preserve">video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obrazki_ai </t>
   </si>
   <si>
     <t xml:space="preserve">system_prompt</t>
@@ -377,40 +380,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -666,708 +677,863 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="125.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="125.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="B9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="B11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="B12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="B14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="B15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="B17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="B21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="B22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="B23" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="B27" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
+      <c r="B28" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="B29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="B31" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="B32" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="B33" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="B34" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="B35" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="B36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="B37" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="s">
+      <c r="B38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="B39" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="B40" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6" t="s">
+      <c r="B41" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="B42" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="7" t="s">
+      <c r="B43" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="B45" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="s">
+      <c r="B47" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B49" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5" t="s">
-        <v>28</v>
+      <c r="B51" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1389,409 +1555,409 @@
   <dimension ref="A1:B53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>72</v>
+      <c r="B1" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>73</v>
+      <c r="B9" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>73</v>
+      <c r="B10" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>73</v>
+      <c r="B11" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>73</v>
+      <c r="B12" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>73</v>
+      <c r="B13" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>73</v>
+      <c r="B14" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>73</v>
+      <c r="B15" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>73</v>
+      <c r="B16" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>73</v>
+      <c r="B17" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>73</v>
+      <c r="B18" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>73</v>
+      <c r="B19" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>73</v>
+      <c r="B20" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>73</v>
+      <c r="B21" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>73</v>
+      <c r="B22" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>73</v>
+      <c r="B23" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>73</v>
+      <c r="B24" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>73</v>
+      <c r="B25" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>73</v>
+      <c r="B26" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>73</v>
+      <c r="B27" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>73</v>
+      <c r="B28" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>73</v>
+      <c r="B29" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>73</v>
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>73</v>
+      <c r="B31" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>73</v>
+      <c r="B32" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>73</v>
+      <c r="B33" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>73</v>
+      <c r="B34" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>73</v>
+      <c r="B35" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>73</v>
+      <c r="B36" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>73</v>
+      <c r="B37" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>73</v>
+      <c r="B38" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>73</v>
+      <c r="B39" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>73</v>
+      <c r="B40" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>73</v>
+      <c r="B41" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>73</v>
+      <c r="B42" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>73</v>
+      <c r="B43" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>73</v>
+      <c r="B44" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>73</v>
+      <c r="B45" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>73</v>
+      <c r="B46" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>73</v>
+      <c r="B47" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>73</v>
+      <c r="B48" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>73</v>
+      <c r="B49" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>73</v>
+      <c r="B50" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>73</v>
+      <c r="B51" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B53" s="8"/>
+      <c r="A53" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="83">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t xml:space="preserve">Remonty - gipsowanie chmur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drzwi5.png</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - wymiana uszczelek w czarnych dziurach</t>
@@ -1155,7 +1158,9 @@
       <c r="B26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="D26" s="5"/>
       <c r="E26" s="3" t="n">
         <v>1</v>
@@ -1169,7 +1174,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1185,7 +1190,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -1201,7 +1206,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -1217,7 +1222,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -1233,7 +1238,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -1249,7 +1254,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -1265,7 +1270,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -1281,7 +1286,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -1297,7 +1302,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -1313,7 +1318,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -1329,7 +1334,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -1345,7 +1350,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -1361,7 +1366,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -1377,7 +1382,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -1393,7 +1398,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -1409,7 +1414,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -1425,7 +1430,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -1441,7 +1446,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -1457,7 +1462,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -1473,7 +1478,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -1489,7 +1494,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -1505,7 +1510,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -1521,7 +1526,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -1537,7 +1542,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -1553,7 +1558,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
@@ -1593,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1646,10 +1651,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1657,10 +1662,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1668,10 +1673,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1679,10 +1684,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1690,10 +1695,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1701,10 +1706,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1712,10 +1717,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1723,10 +1728,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1734,10 +1739,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1745,10 +1750,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1756,10 +1761,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1767,10 +1772,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1778,10 +1783,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1789,10 +1794,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1800,10 +1805,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1811,10 +1816,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1822,10 +1827,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1833,10 +1838,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1844,10 +1849,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1855,10 +1860,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1866,10 +1871,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1877,10 +1882,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1888,10 +1893,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1899,10 +1904,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1910,10 +1915,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1921,10 +1926,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1932,10 +1937,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1943,10 +1948,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1954,10 +1959,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1965,10 +1970,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1976,10 +1981,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1987,10 +1992,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1998,10 +2003,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2009,10 +2014,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2020,10 +2025,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2031,10 +2036,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2042,10 +2047,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2053,10 +2058,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2064,10 +2069,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2075,10 +2080,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2086,10 +2091,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2097,10 +2102,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2108,10 +2113,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2119,7 +2124,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="85">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -35,6 +35,9 @@
     <t xml:space="preserve">video</t>
   </si>
   <si>
+    <t xml:space="preserve">obrazki_ai</t>
+  </si>
+  <si>
     <t xml:space="preserve">system_prompt</t>
   </si>
   <si>
@@ -74,7 +77,7 @@
     <t xml:space="preserve">4.png</t>
   </si>
   <si>
-    <t xml:space="preserve">4.mp4,e.pdf</t>
+    <t xml:space="preserve">4.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Egzamin ze znajomości przepisów niebieskich</t>
@@ -83,7 +86,7 @@
     <t xml:space="preserve">5.png</t>
   </si>
   <si>
-    <t xml:space="preserve">5.mp4,e.pdf</t>
+    <t xml:space="preserve">5.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Oczekiwanie na przydział do pracy</t>
@@ -92,19 +95,22 @@
     <t xml:space="preserve">6.png</t>
   </si>
   <si>
-    <t xml:space="preserve">6.mp4,e.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przydział do brygady remontowej — pierwsze narzędzia</t>
+    <t xml:space="preserve">6.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powrót na ziemie, reinkarnacja</t>
   </si>
   <si>
     <t xml:space="preserve">7.png</t>
   </si>
   <si>
-    <t xml:space="preserve">7.mp4,e.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remonty - wyrównywanie poziomów chmur</t>
+    <t xml:space="preserve">7.mp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wysłannik z nieba odpowiada- wyrównywanie poziomów chmur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Jesteś Pawłem — zmarłym robotnikiem niebieskim w trakcie kosmicznego remontu. Piszesz po polsku. Ton: absurdalny, z humorem robotniczym. Odpowiedź maksymalnie 5 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Westchnij ile dni jesteś w niebie licząc od {data_smierci_str}. Nie wspominaj Księgi Urantii.</t>
@@ -279,7 +285,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,12 +321,18 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -401,7 +413,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -422,7 +434,11 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -430,7 +446,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -442,7 +458,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -722,11 +738,11 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="n">
-        <v>1</v>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -734,39 +750,39 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -774,39 +790,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
+      <c r="D5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -814,39 +830,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>8</v>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -854,35 +870,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>28</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -890,31 +908,33 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>28</v>
+      <c r="B11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -922,31 +942,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>28</v>
+      <c r="B13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -954,31 +974,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>28</v>
+      <c r="B15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -986,31 +1006,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>28</v>
+      <c r="B17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1018,31 +1038,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>28</v>
+      <c r="B19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1050,69 +1070,69 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>42</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>43</v>
+      <c r="B22" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>42</v>
+      <c r="B23" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1120,35 +1140,35 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D24" s="5"/>
-      <c r="E24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>42</v>
+      <c r="E24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>42</v>
+      <c r="B25" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1156,33 +1176,33 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D26" s="5"/>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>28</v>
+      <c r="B27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1190,31 +1210,31 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>28</v>
+      <c r="B29" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1222,31 +1242,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>28</v>
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1254,31 +1274,31 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>28</v>
+      <c r="B33" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1286,31 +1306,31 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>28</v>
+      <c r="B35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1318,31 +1338,31 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>28</v>
+      <c r="B37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1350,31 +1370,31 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>28</v>
+      <c r="B39" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1382,31 +1402,31 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>28</v>
+      <c r="B41" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1414,31 +1434,31 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="n">
+      <c r="A43" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>28</v>
+      <c r="B43" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1446,31 +1466,31 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="n">
+      <c r="A45" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>28</v>
+      <c r="B45" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1478,31 +1498,31 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="n">
+      <c r="A47" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>28</v>
+      <c r="B47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1510,31 +1530,31 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="n">
+      <c r="A49" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>28</v>
+      <c r="B49" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1542,31 +1562,31 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="n">
+      <c r="A51" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>28</v>
+      <c r="B51" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1598,10 +1618,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1611,10 +1631,10 @@
       <c r="B2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
@@ -1623,10 +1643,10 @@
       <c r="B4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
@@ -1635,10 +1655,10 @@
       <c r="B6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
@@ -1647,14 +1667,14 @@
       <c r="B8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>80</v>
+      <c r="B9" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1662,21 +1682,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>80</v>
+      <c r="B11" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1684,21 +1704,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>80</v>
+      <c r="B13" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1706,21 +1726,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>80</v>
+      <c r="B15" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1728,21 +1748,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>80</v>
+      <c r="B17" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1750,21 +1770,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>80</v>
+      <c r="B19" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1772,21 +1792,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>80</v>
+      <c r="B21" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1794,21 +1814,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>80</v>
+      <c r="B23" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1816,21 +1836,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>80</v>
+      <c r="B25" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1838,21 +1858,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>80</v>
+      <c r="B27" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1860,21 +1880,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>80</v>
+      <c r="B29" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1882,21 +1902,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>80</v>
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1904,21 +1924,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>80</v>
+      <c r="B33" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1926,21 +1946,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>80</v>
+      <c r="B35" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1948,21 +1968,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>80</v>
+      <c r="B37" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1970,21 +1990,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>80</v>
+      <c r="B39" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1992,21 +2012,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="n">
+      <c r="A41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>80</v>
+      <c r="B41" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2014,21 +2034,21 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="n">
+      <c r="A43" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>80</v>
+      <c r="B43" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2036,21 +2056,21 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="n">
+      <c r="A45" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>80</v>
+      <c r="B45" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2058,21 +2078,21 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="n">
+      <c r="A47" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>80</v>
+      <c r="B47" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2080,21 +2100,21 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="n">
+      <c r="A49" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>80</v>
+      <c r="B49" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2102,21 +2122,21 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="n">
+      <c r="A51" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>80</v>
+      <c r="B51" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2124,14 +2144,14 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="n">
+      <c r="A53" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="10"/>
+      <c r="B53" s="11"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="n">
@@ -2139,7 +2159,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="n">
+      <c r="A55" s="7" t="n">
         <v>54</v>
       </c>
     </row>
@@ -2149,7 +2169,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="n">
+      <c r="A57" s="7" t="n">
         <v>56</v>
       </c>
     </row>
@@ -2159,7 +2179,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="n">
+      <c r="A59" s="7" t="n">
         <v>58</v>
       </c>
     </row>
@@ -2169,7 +2189,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="n">
+      <c r="A61" s="7" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2179,7 +2199,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="n">
+      <c r="A63" s="7" t="n">
         <v>62</v>
       </c>
     </row>
@@ -2189,7 +2209,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="n">
+      <c r="A65" s="7" t="n">
         <v>64</v>
       </c>
     </row>
@@ -2199,7 +2219,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="n">
+      <c r="A67" s="7" t="n">
         <v>66</v>
       </c>
     </row>
@@ -2209,7 +2229,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="n">
+      <c r="A69" s="7" t="n">
         <v>68</v>
       </c>
     </row>
@@ -2219,7 +2239,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="n">
+      <c r="A71" s="7" t="n">
         <v>70</v>
       </c>
     </row>
@@ -2229,7 +2249,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="n">
+      <c r="A73" s="7" t="n">
         <v>72</v>
       </c>
     </row>
@@ -2239,7 +2259,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6" t="n">
+      <c r="A75" s="7" t="n">
         <v>74</v>
       </c>
     </row>
@@ -2249,7 +2269,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="n">
+      <c r="A77" s="7" t="n">
         <v>76</v>
       </c>
     </row>
@@ -2259,7 +2279,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6" t="n">
+      <c r="A79" s="7" t="n">
         <v>78</v>
       </c>
     </row>
@@ -2269,7 +2289,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="n">
+      <c r="A81" s="7" t="n">
         <v>80</v>
       </c>
     </row>
@@ -2279,7 +2299,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="6" t="n">
+      <c r="A83" s="7" t="n">
         <v>82</v>
       </c>
     </row>
@@ -2289,7 +2309,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6" t="n">
+      <c r="A85" s="7" t="n">
         <v>84</v>
       </c>
     </row>
@@ -2299,7 +2319,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6" t="n">
+      <c r="A87" s="7" t="n">
         <v>86</v>
       </c>
     </row>
@@ -2309,7 +2329,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6" t="n">
+      <c r="A89" s="7" t="n">
         <v>88</v>
       </c>
     </row>
@@ -2319,7 +2339,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6" t="n">
+      <c r="A91" s="7" t="n">
         <v>90</v>
       </c>
     </row>
@@ -2329,7 +2349,7 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6" t="n">
+      <c r="A93" s="7" t="n">
         <v>92</v>
       </c>
     </row>
@@ -2339,7 +2359,7 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6" t="n">
+      <c r="A95" s="7" t="n">
         <v>94</v>
       </c>
     </row>
@@ -2349,7 +2369,7 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6" t="n">
+      <c r="A97" s="7" t="n">
         <v>96</v>
       </c>
     </row>
@@ -2359,7 +2379,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6" t="n">
+      <c r="A99" s="7" t="n">
         <v>98</v>
       </c>
     </row>
@@ -2369,7 +2389,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="n">
+      <c r="A101" s="7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2379,7 +2399,7 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6" t="n">
+      <c r="A103" s="7" t="n">
         <v>102</v>
       </c>
     </row>
@@ -2389,7 +2409,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6" t="n">
+      <c r="A105" s="7" t="n">
         <v>104</v>
       </c>
     </row>
@@ -2399,7 +2419,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6" t="n">
+      <c r="A107" s="7" t="n">
         <v>106</v>
       </c>
     </row>
@@ -2409,7 +2429,7 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6" t="n">
+      <c r="A109" s="7" t="n">
         <v>108</v>
       </c>
     </row>
@@ -2419,7 +2439,7 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="6" t="n">
+      <c r="A111" s="7" t="n">
         <v>110</v>
       </c>
     </row>
@@ -2429,7 +2449,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6" t="n">
+      <c r="A113" s="7" t="n">
         <v>112</v>
       </c>
     </row>
@@ -2439,7 +2459,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="6" t="n">
+      <c r="A115" s="7" t="n">
         <v>114</v>
       </c>
     </row>
@@ -2449,7 +2469,7 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="6" t="n">
+      <c r="A117" s="7" t="n">
         <v>116</v>
       </c>
     </row>
@@ -2459,7 +2479,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="6" t="n">
+      <c r="A119" s="7" t="n">
         <v>118</v>
       </c>
     </row>
@@ -2469,7 +2489,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="6" t="n">
+      <c r="A121" s="7" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2479,7 +2499,7 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="6" t="n">
+      <c r="A123" s="7" t="n">
         <v>122</v>
       </c>
     </row>
@@ -2489,7 +2509,7 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="6" t="n">
+      <c r="A125" s="7" t="n">
         <v>124</v>
       </c>
     </row>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -1641,7 +1641,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="66.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="87">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t xml:space="preserve">styl_kosmiczny.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">requiem_styl_Odpowiedzi_tekstowej_1_7.txt</t>
   </si>
   <si>
     <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_system.txt</t>
@@ -1075,7 +1078,6 @@
       <c r="B20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="0"/>
       <c r="D20" s="5"/>
       <c r="E20" s="6" t="n">
         <v>1</v>
@@ -1091,7 +1093,6 @@
       <c r="B21" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="0"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="n">
         <v>1</v>
@@ -1107,7 +1108,6 @@
       <c r="B22" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="0"/>
       <c r="D22" s="5"/>
       <c r="E22" s="6" t="n">
         <v>1</v>
@@ -1641,7 +1641,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="66.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="66.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1659,43 +1659,78 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6"/>
+      <c r="B3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
@@ -1705,7 +1740,7 @@
         <v>83</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1716,7 +1751,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1727,7 +1762,7 @@
         <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1738,7 +1773,7 @@
         <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1749,7 +1784,7 @@
         <v>83</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1760,7 +1795,7 @@
         <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1771,7 +1806,7 @@
         <v>83</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1782,7 +1817,7 @@
         <v>83</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1793,7 +1828,7 @@
         <v>83</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1804,7 +1839,7 @@
         <v>83</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1815,7 +1850,7 @@
         <v>83</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1826,7 +1861,7 @@
         <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1837,7 +1872,7 @@
         <v>83</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1848,7 +1883,7 @@
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1859,7 +1894,7 @@
         <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1870,7 +1905,7 @@
         <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1881,7 +1916,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1892,7 +1927,7 @@
         <v>83</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1903,7 +1938,7 @@
         <v>83</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1914,7 +1949,7 @@
         <v>83</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1925,7 +1960,7 @@
         <v>83</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1936,7 +1971,7 @@
         <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1947,7 +1982,7 @@
         <v>83</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1958,7 +1993,7 @@
         <v>83</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1969,7 +2004,7 @@
         <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1980,7 +2015,7 @@
         <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1991,7 +2026,7 @@
         <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2002,7 +2037,7 @@
         <v>83</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2013,7 +2048,7 @@
         <v>83</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2024,7 +2059,7 @@
         <v>83</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2035,7 +2070,7 @@
         <v>83</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2046,7 +2081,7 @@
         <v>83</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2057,7 +2092,7 @@
         <v>83</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2068,7 +2103,7 @@
         <v>83</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2079,7 +2114,7 @@
         <v>83</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2090,7 +2125,7 @@
         <v>83</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2101,7 +2136,7 @@
         <v>83</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2112,7 +2147,7 @@
         <v>83</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2123,7 +2158,7 @@
         <v>83</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2134,7 +2169,7 @@
         <v>83</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2145,7 +2180,7 @@
         <v>83</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2156,7 +2191,7 @@
         <v>83</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2167,7 +2202,7 @@
         <v>83</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2175,7 +2210,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="89">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -167,18 +167,18 @@
     <t xml:space="preserve">Remonty - montaż rynien na Księżycu</t>
   </si>
   <si>
+    <t xml:space="preserve">Remonty - tapetowanie czarnej dziury</t>
+  </si>
+  <si>
     <t xml:space="preserve">drzwi4.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Remonty - tapetowanie czarnej dziury</t>
+    <t xml:space="preserve">Remonty - gipsowanie chmur</t>
   </si>
   <si>
     <t xml:space="preserve">drzwi5.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Remonty - gipsowanie chmur</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remonty - wymiana uszczelek w czarnych dziurach</t>
   </si>
   <si>
@@ -233,7 +233,13 @@
     <t xml:space="preserve">Remonty - instalacja klimatyzacji w Piekle</t>
   </si>
   <si>
+    <t xml:space="preserve">drzwi10.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Remonty - remont tunelu czasoprzestrzennego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drzwi11.png</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - czyszczenie filtrów w mgławicach</t>
@@ -1141,9 +1147,7 @@
       <c r="B24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="C24" s="0"/>
       <c r="D24" s="5"/>
       <c r="E24" s="6" t="n">
         <v>1</v>
@@ -1157,10 +1161,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="n">
@@ -1175,10 +1179,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="6" t="n">
@@ -1196,7 +1200,7 @@
         <v>52</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="n">
@@ -1214,7 +1218,7 @@
         <v>53</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="6" t="n">
@@ -1322,7 +1326,7 @@
         <v>63</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="6" t="n">
@@ -1340,7 +1344,7 @@
         <v>64</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="n">
@@ -1357,8 +1361,8 @@
       <c r="B36" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>46</v>
+      <c r="C36" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="6" t="n">
@@ -1375,8 +1379,8 @@
       <c r="B37" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>48</v>
+      <c r="C37" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="n">
@@ -1393,8 +1397,8 @@
       <c r="B38" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>50</v>
+      <c r="C38" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="6" t="n">
@@ -1411,8 +1415,8 @@
       <c r="B39" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>55</v>
+      <c r="C39" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="n">
@@ -1430,7 +1434,7 @@
         <v>69</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="6" t="n">
@@ -1445,10 +1449,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>59</v>
+        <v>71</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>72</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="n">
@@ -1463,11 +1467,9 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>61</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="C42" s="0"/>
       <c r="D42" s="5"/>
       <c r="E42" s="6" t="n">
         <v>1</v>
@@ -1481,9 +1483,9 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="C43" s="0"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="n">
         <v>1</v>
@@ -1497,9 +1499,9 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="C44" s="0"/>
       <c r="D44" s="5"/>
       <c r="E44" s="6" t="n">
         <v>1</v>
@@ -1513,7 +1515,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
@@ -1529,7 +1531,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -1545,7 +1547,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
@@ -1561,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -1577,7 +1579,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
@@ -1593,7 +1595,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
@@ -1609,7 +1611,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
@@ -1649,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1660,10 +1662,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1671,10 +1673,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1682,10 +1684,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1693,10 +1695,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1704,10 +1706,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1715,10 +1717,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1726,10 +1728,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1737,10 +1739,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1748,10 +1750,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1759,10 +1761,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1770,10 +1772,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1781,10 +1783,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1792,10 +1794,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1803,10 +1805,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1814,10 +1816,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1825,10 +1827,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1836,10 +1838,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1847,10 +1849,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1858,10 +1860,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1869,10 +1871,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1880,10 +1882,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1891,10 +1893,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1902,10 +1904,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1913,10 +1915,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1924,10 +1926,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1935,10 +1937,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1946,10 +1948,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1957,10 +1959,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1968,10 +1970,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1979,10 +1981,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1990,10 +1992,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2001,10 +2003,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2012,10 +2014,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2023,10 +2025,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2034,10 +2036,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2045,10 +2047,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2056,10 +2058,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2067,10 +2069,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2078,10 +2080,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2089,10 +2091,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2100,10 +2102,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2111,10 +2113,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2122,10 +2124,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2133,10 +2135,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2144,10 +2146,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2155,10 +2157,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2166,10 +2168,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2177,10 +2179,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2188,10 +2190,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2199,10 +2201,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2210,7 +2212,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="89">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -50,9 +50,6 @@
     <t xml:space="preserve">1.mp4</t>
   </si>
   <si>
-    <t xml:space="preserve">Jesteś Pawłem — zmarłym mężczyzną piszącym z zaświatów. Piszesz po polsku. Ton: spokojny, lekko absurdalny, z humorem. Odpowiedź maksymalnie 5 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Wspomnij że umarłeś na suchoty dnia {data_smierci_str}. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Nie wspominaj Księgi Urantii.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Orientacja w przestrzeni pozagrobowej</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t xml:space="preserve">Wysłannik z nieba odpowiada- wyrównywanie poziomów chmur</t>
   </si>
   <si>
-    <t xml:space="preserve">Jesteś Pawłem — zmarłym robotnikiem niebieskim w trakcie kosmicznego remontu. Piszesz po polsku. Ton: absurdalny, z humorem robotniczym. Odpowiedź maksymalnie 5 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Westchnij ile dni jesteś w niebie licząc od {data_smierci_str}. Nie wspominaj Księgi Urantii.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remonty - malowanie nieba na właściwy odcień błękitu</t>
   </si>
   <si>
@@ -161,9 +155,6 @@
     <t xml:space="preserve">e.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Jesteś Pawłem — zmarłym robotnikiem niebieskim w trakcie kosmicznego remontu. Piszesz po polsku. Ton: absurdalny, z humorem robotniczym. Odpowiedź maksymalnie 10 zdań. Podpisz się: — Autoresponder Pawła-zza-światów. Nawiąż do wiadomości tej osoby paradoksalnie chwaląc że na Ziemi jest lepiej niż w niebie. Westchnij ile dni jesteś w niebie licząc od {data_smierci_str}. Nie wspominaj Księgi Urantii. Zapytaj czy ona też zaczyna jakieś remonty u siebie? Jeżeli nadawcą jest Ania to wesprzyją ją radą w sprawach budowlanych (wstawiania drzwi wewnętrznych) i chwal remontowanie jako mądre. Daj jej jednak bardzo złe rady które by nie pomogły w remoncie lecz będą tak absurdalnie niedorzeczne że śmieszne.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remonty - montaż rynien na Księżycu</t>
   </si>
   <si>
@@ -245,6 +236,9 @@
     <t xml:space="preserve">Remonty - czyszczenie filtrów w mgławicach</t>
   </si>
   <si>
+    <t xml:space="preserve">drzwi12.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Remonty - polerowanie meteorytów</t>
   </si>
   <si>
@@ -288,6 +282,9 @@
   </si>
   <si>
     <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_system.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">requiem_budowlaniec_drzwi.txt</t>
   </si>
   <si>
     <t xml:space="preserve">requiem_WYSLANNIK_system_8_.txt</t>
@@ -776,858 +773,761 @@
       <c r="E2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="E7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="5"/>
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="E23" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="71.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F39" s="9"/>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="9" t="s">
-        <v>46</v>
-      </c>
+      <c r="F40" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="F50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="F51" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1658,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1669,10 +1569,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1680,10 +1580,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1691,10 +1591,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1702,10 +1602,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1713,10 +1613,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1724,10 +1624,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1735,10 +1635,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1746,10 +1646,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1757,10 +1657,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1768,10 +1668,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1779,10 +1679,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1790,10 +1690,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1801,10 +1701,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1812,10 +1712,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1823,10 +1723,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1834,10 +1734,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1845,10 +1745,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1856,10 +1756,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1867,10 +1767,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1878,10 +1778,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1889,10 +1789,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1900,10 +1800,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1911,10 +1811,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1922,10 +1822,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1933,10 +1833,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1944,10 +1844,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1955,10 +1855,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1966,10 +1866,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1977,10 +1877,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1988,10 +1888,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1999,10 +1899,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2010,10 +1910,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2021,10 +1921,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2032,10 +1932,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2043,10 +1943,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2054,10 +1954,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2065,10 +1965,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2076,10 +1976,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2087,10 +1987,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2098,10 +1998,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2109,10 +2009,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2120,10 +2020,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2131,10 +2031,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2142,10 +2042,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2153,10 +2053,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2164,10 +2064,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2175,10 +2075,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2186,10 +2086,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2197,10 +2097,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2208,10 +2108,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2219,7 +2119,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -35,10 +35,10 @@
     <t xml:space="preserve">video</t>
   </si>
   <si>
-    <t xml:space="preserve">obrazki_ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">system_prompt</t>
+    <t xml:space="preserve">kompresja_jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ilosc_obrazkow_ai </t>
   </si>
   <si>
     <t xml:space="preserve">Przybycie do zaświatów — odprawa celna</t>
@@ -297,7 +297,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,6 +338,13 @@
       <charset val="238"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -359,7 +366,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,12 +389,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF996600"/>
-        <bgColor rgb="FF993300"/>
       </patternFill>
     </fill>
   </fills>
@@ -442,19 +443,23 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -462,15 +467,11 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -496,7 +497,7 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF996600"/>
+      <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
@@ -734,7 +735,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="125.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -753,781 +754,881 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5"/>
+      <c r="E2" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6"/>
+      <c r="E3" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+    </row>
+    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="71.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F25" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="5" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="B26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="B27" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="B28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="B29" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="B31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="B32" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="B33" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="B35" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="s">
+      <c r="B36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="B37" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="B39" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="B40" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" customFormat="false" ht="71.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="9"/>
-    </row>
-    <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="9"/>
-    </row>
-    <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="9"/>
-    </row>
-    <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>68</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="6"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="5"/>
-      <c r="E42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="5"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="6"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="5"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="6"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="5"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="6"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="5"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="6"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="5"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="6"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1565,10 +1666,10 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1576,10 +1677,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1587,10 +1688,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1598,10 +1699,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1609,10 +1710,10 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1620,10 +1721,10 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1631,10 +1732,10 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1642,10 +1743,10 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1653,10 +1754,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1664,10 +1765,10 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1675,10 +1776,10 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1686,10 +1787,10 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1697,10 +1798,10 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1708,10 +1809,10 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1719,10 +1820,10 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1730,10 +1831,10 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -1741,10 +1842,10 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -1752,10 +1853,10 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -1763,10 +1864,10 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -1774,10 +1875,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -1785,10 +1886,10 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -1796,10 +1897,10 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -1807,10 +1908,10 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -1818,10 +1919,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -1829,10 +1930,10 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -1840,10 +1941,10 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -1851,10 +1952,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -1862,10 +1963,10 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -1873,10 +1974,10 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -1884,10 +1985,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -1895,10 +1996,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -1906,10 +2007,10 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -1917,10 +2018,10 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -1928,10 +2029,10 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -1939,10 +2040,10 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -1950,10 +2051,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -1961,10 +2062,10 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -1972,10 +2073,10 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -1983,10 +2084,10 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -1994,10 +2095,10 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -2005,10 +2106,10 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -2016,10 +2117,10 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -2027,10 +2128,10 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -2038,10 +2139,10 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -2049,10 +2150,10 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -2060,10 +2161,10 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -2071,10 +2172,10 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -2082,10 +2183,10 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -2093,10 +2194,10 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -2104,10 +2205,10 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -2115,7 +2216,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="5" t="n">
         <v>51</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -2123,373 +2224,373 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="8" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="11"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="5" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="8" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="5" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="8" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="5" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="8" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="5" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="8" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="5" t="n">
         <v>61</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="8" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="5" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n">
+      <c r="A65" s="8" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="5" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="8" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="5" t="n">
         <v>67</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="n">
+      <c r="A69" s="8" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n">
+      <c r="A71" s="8" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="5" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
+      <c r="A73" s="8" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="5" t="n">
         <v>73</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="n">
+      <c r="A75" s="8" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="5" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
+      <c r="A77" s="8" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="5" t="n">
         <v>77</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
+      <c r="A79" s="8" t="n">
         <v>78</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
+      <c r="A80" s="5" t="n">
         <v>79</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="n">
+      <c r="A81" s="8" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="5" t="n">
         <v>81</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="n">
+      <c r="A83" s="8" t="n">
         <v>82</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="n">
+      <c r="A84" s="5" t="n">
         <v>83</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="n">
+      <c r="A85" s="8" t="n">
         <v>84</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="5" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="n">
+      <c r="A87" s="8" t="n">
         <v>86</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="5" t="n">
         <v>87</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="n">
+      <c r="A89" s="8" t="n">
         <v>88</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="n">
+      <c r="A90" s="5" t="n">
         <v>89</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7" t="n">
+      <c r="A91" s="8" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="n">
+      <c r="A92" s="5" t="n">
         <v>91</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7" t="n">
+      <c r="A93" s="8" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="5" t="n">
         <v>93</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7" t="n">
+      <c r="A95" s="8" t="n">
         <v>94</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
+      <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7" t="n">
+      <c r="A97" s="8" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="n">
+      <c r="A98" s="5" t="n">
         <v>97</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7" t="n">
+      <c r="A99" s="8" t="n">
         <v>98</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="n">
+      <c r="A100" s="5" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7" t="n">
+      <c r="A101" s="8" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="n">
+      <c r="A102" s="5" t="n">
         <v>101</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="n">
+      <c r="A103" s="8" t="n">
         <v>102</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4" t="n">
+      <c r="A104" s="5" t="n">
         <v>103</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7" t="n">
+      <c r="A105" s="8" t="n">
         <v>104</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="4" t="n">
+      <c r="A106" s="5" t="n">
         <v>105</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7" t="n">
+      <c r="A107" s="8" t="n">
         <v>106</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="n">
+      <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7" t="n">
+      <c r="A109" s="8" t="n">
         <v>108</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="n">
+      <c r="A110" s="5" t="n">
         <v>109</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7" t="n">
+      <c r="A111" s="8" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="4" t="n">
+      <c r="A112" s="5" t="n">
         <v>111</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7" t="n">
+      <c r="A113" s="8" t="n">
         <v>112</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="4" t="n">
+      <c r="A114" s="5" t="n">
         <v>113</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="7" t="n">
+      <c r="A115" s="8" t="n">
         <v>114</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="4" t="n">
+      <c r="A116" s="5" t="n">
         <v>115</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="7" t="n">
+      <c r="A117" s="8" t="n">
         <v>116</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="4" t="n">
+      <c r="A118" s="5" t="n">
         <v>117</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7" t="n">
+      <c r="A119" s="8" t="n">
         <v>118</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="4" t="n">
+      <c r="A120" s="5" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="7" t="n">
+      <c r="A121" s="8" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="4" t="n">
+      <c r="A122" s="5" t="n">
         <v>121</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7" t="n">
+      <c r="A123" s="8" t="n">
         <v>122</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="4" t="n">
+      <c r="A124" s="5" t="n">
         <v>123</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="7" t="n">
+      <c r="A125" s="8" t="n">
         <v>124</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="4" t="n">
+      <c r="A126" s="5" t="n">
         <v>125</v>
       </c>
     </row>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -1170,7 +1170,7 @@
         <v>43</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>4</v>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -832,7 +832,7 @@
         <v>90</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -852,7 +852,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1133,7 +1133,7 @@
         <v>90</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="71.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1150,7 +1150,7 @@
         <v>90</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1170,7 +1170,7 @@
         <v>70</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -772,7 +772,7 @@
         <v>90</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -791,8 +791,8 @@
       <c r="E3" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <v>1</v>
+      <c r="F3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -812,7 +812,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -831,8 +831,8 @@
       <c r="E5" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F5" s="7" t="n">
-        <v>1</v>
+      <c r="F5" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -852,7 +852,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -871,8 +871,8 @@
       <c r="E7" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F7" s="7" t="n">
-        <v>1</v>
+      <c r="F7" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -892,7 +892,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -907,8 +907,8 @@
       <c r="E9" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>1</v>
+      <c r="F9" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -924,7 +924,7 @@
         <v>90</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -939,8 +939,8 @@
       <c r="E11" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F11" s="7" t="n">
-        <v>1</v>
+      <c r="F11" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -956,7 +956,7 @@
         <v>90</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -971,8 +971,8 @@
       <c r="E13" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F13" s="7" t="n">
-        <v>1</v>
+      <c r="F13" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -988,7 +988,7 @@
         <v>90</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1003,8 +1003,8 @@
       <c r="E15" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>1</v>
+      <c r="F15" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1020,7 +1020,7 @@
         <v>90</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1035,8 +1035,8 @@
       <c r="E17" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F17" s="7" t="n">
-        <v>1</v>
+      <c r="F17" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1052,7 +1052,7 @@
         <v>90</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1067,8 +1067,8 @@
       <c r="E19" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F19" s="7" t="n">
-        <v>1</v>
+      <c r="F19" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1083,7 +1083,7 @@
         <v>90</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1097,8 +1097,8 @@
       <c r="E21" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F21" s="7" t="n">
-        <v>1</v>
+      <c r="F21" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1113,7 +1113,7 @@
         <v>90</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1132,8 +1132,8 @@
       <c r="E23" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F23" s="7" t="n">
-        <v>1</v>
+      <c r="F23" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="71.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1150,7 +1150,7 @@
         <v>90</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1169,8 +1169,8 @@
       <c r="E25" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="F25" s="7" t="n">
-        <v>1</v>
+      <c r="F25" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1190,7 +1190,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1209,8 +1209,8 @@
       <c r="E27" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F27" s="7" t="n">
-        <v>3</v>
+      <c r="F27" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1247,7 +1247,7 @@
       <c r="E29" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       <c r="E31" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       <c r="E33" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1355,8 +1355,8 @@
       <c r="E35" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F35" s="7" t="n">
-        <v>1</v>
+      <c r="F35" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1374,7 +1374,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1391,8 +1391,8 @@
       <c r="E37" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F37" s="7" t="n">
-        <v>1</v>
+      <c r="F37" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1410,7 +1410,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1427,8 +1427,8 @@
       <c r="E39" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F39" s="7" t="n">
-        <v>1</v>
+      <c r="F39" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1446,7 +1446,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1463,8 +1463,8 @@
       <c r="E41" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F41" s="7" t="n">
-        <v>1</v>
+      <c r="F41" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1482,7 +1482,7 @@
         <v>90</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1496,8 +1496,8 @@
       <c r="E43" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F43" s="7" t="n">
-        <v>1</v>
+      <c r="F43" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1512,7 +1512,7 @@
         <v>90</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1527,8 +1527,8 @@
       <c r="E45" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F45" s="7" t="n">
-        <v>1</v>
+      <c r="F45" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1544,7 +1544,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1559,8 +1559,8 @@
       <c r="E47" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F47" s="7" t="n">
-        <v>1</v>
+      <c r="F47" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1576,7 +1576,7 @@
         <v>90</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1591,8 +1591,8 @@
       <c r="E49" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F49" s="7" t="n">
-        <v>1</v>
+      <c r="F49" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1608,7 +1608,7 @@
         <v>90</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1623,8 +1623,8 @@
       <c r="E51" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F51" s="7" t="n">
-        <v>1</v>
+      <c r="F51" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -760,7 +760,7 @@
         <v>90</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -780,7 +780,7 @@
         <v>90</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -800,7 +800,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -820,7 +820,7 @@
         <v>90</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -840,7 +840,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -860,7 +860,7 @@
         <v>90</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -880,7 +880,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="117">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -59,6 +59,18 @@
     <t xml:space="preserve">2.mp4</t>
   </si>
   <si>
+    <t xml:space="preserve">Wartość</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co oznacza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozmiar pliku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Użycie</t>
+  </si>
+  <si>
     <t xml:space="preserve">Przydział do strefy czyśćcowej sektor B</t>
   </si>
   <si>
@@ -68,6 +80,15 @@
     <t xml:space="preserve">3.mp4</t>
   </si>
   <si>
+    <t xml:space="preserve">PNG bez kompresji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bardzo duży (~500KB-2MB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdy chcesz najlepszą jakość</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pierwsze zajęcia z medytacji transcendentnej</t>
   </si>
   <si>
@@ -77,6 +98,18 @@
     <t xml:space="preserve">4.mp4</t>
   </si>
   <si>
+    <t xml:space="preserve">10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bardzo niska jakość JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bardzo mały (~30-50KB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gdy trzeba zaoszczędzić miejsce</t>
+  </si>
+  <si>
     <t xml:space="preserve">Egzamin ze znajomości przepisów niebieskich</t>
   </si>
   <si>
@@ -86,6 +119,18 @@
     <t xml:space="preserve">5.mp4</t>
   </si>
   <si>
+    <t xml:space="preserve">30-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niska jakość JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mały (~50-100KB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szybkie wysyłanie</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oczekiwanie na przydział do pracy</t>
   </si>
   <si>
@@ -95,6 +140,18 @@
     <t xml:space="preserve">6.mp4</t>
   </si>
   <si>
+    <t xml:space="preserve">50-60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Średnia jakość JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Średni (~100-200KB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance jakość/rozmiar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Powrót na ziemie, reinkarnacja</t>
   </si>
   <si>
@@ -104,7 +161,31 @@
     <t xml:space="preserve">7.mp4</t>
   </si>
   <si>
+    <t xml:space="preserve">70-80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dobra jakość JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Większy (~200-400KB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Można widać różnicę</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wysłannik z nieba odpowiada- wyrównywanie poziomów chmur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bardzo dobra jakość JPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duży (~400-700KB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prawie jak PNG</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - malowanie nieba na właściwy odcień błękitu</t>
@@ -300,7 +381,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,6 +439,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -421,7 +510,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -456,6 +545,18 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -718,7 +819,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -727,6 +828,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -788,25 +891,49 @@
       <c r="F3" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="H3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="10" t="n">
         <v>0</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -814,19 +941,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -834,19 +973,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>50</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -854,19 +1005,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>90</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>1</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -874,19 +1037,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>90</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>1</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -894,7 +1069,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="6"/>
@@ -904,13 +1079,25 @@
       <c r="F9" s="6" t="n">
         <v>1</v>
       </c>
+      <c r="H9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -926,7 +1113,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -942,7 +1129,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -958,7 +1145,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -974,7 +1161,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -990,7 +1177,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1006,7 +1193,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1022,7 +1209,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -1038,7 +1225,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1054,7 +1241,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -1070,7 +1257,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="7" t="n">
@@ -1085,7 +1272,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7" t="n">
@@ -1099,8 +1286,8 @@
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>40</v>
+      <c r="B22" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="7" t="n">
@@ -1114,14 +1301,14 @@
       <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>41</v>
+      <c r="B23" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>90</v>
@@ -1135,10 +1322,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>90</v>
@@ -1152,13 +1339,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>70</v>
@@ -1172,13 +1359,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>90</v>
@@ -1192,13 +1379,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>90</v>
@@ -1212,13 +1399,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>90</v>
@@ -1232,10 +1419,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7" t="n">
@@ -1250,10 +1437,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="7" t="n">
@@ -1268,10 +1455,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="n">
@@ -1286,10 +1473,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="7" t="n">
@@ -1304,10 +1491,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7" t="n">
@@ -1322,10 +1509,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="7" t="n">
@@ -1340,10 +1527,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7" t="n">
@@ -1358,10 +1545,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="7" t="n">
@@ -1376,10 +1563,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7" t="n">
@@ -1394,10 +1581,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="7" t="n">
@@ -1412,10 +1599,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="7" t="n">
@@ -1430,10 +1617,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="7" t="n">
@@ -1448,10 +1635,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="7" t="n">
@@ -1466,10 +1653,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="7" t="n">
@@ -1484,7 +1671,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7" t="n">
@@ -1499,7 +1686,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="7" t="n">
@@ -1514,7 +1701,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1530,7 +1717,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
@@ -1546,7 +1733,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -1562,7 +1749,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
@@ -1578,7 +1765,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -1594,7 +1781,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -1610,7 +1797,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -1650,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>82</v>
+        <v>108</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1661,10 +1848,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1672,10 +1859,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1683,10 +1870,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1694,10 +1881,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1705,10 +1892,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1716,10 +1903,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1727,10 +1914,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1738,10 +1925,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1749,10 +1936,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1760,10 +1947,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1771,10 +1958,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1782,10 +1969,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1793,10 +1980,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1804,10 +1991,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1815,10 +2002,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1826,10 +2013,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1837,10 +2024,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1848,10 +2035,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1859,10 +2046,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1870,10 +2057,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1881,10 +2068,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1892,10 +2079,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1903,10 +2090,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1914,10 +2101,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1925,10 +2112,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1936,10 +2123,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1947,10 +2134,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1958,10 +2145,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1969,10 +2156,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1980,10 +2167,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1991,10 +2178,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2002,10 +2189,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2013,10 +2200,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2024,10 +2211,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2035,10 +2222,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2046,10 +2233,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2057,10 +2244,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2068,10 +2255,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2079,10 +2266,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2090,10 +2277,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2101,10 +2288,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2112,10 +2299,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2123,10 +2310,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2134,10 +2321,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2145,10 +2332,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2156,10 +2343,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2167,10 +2354,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2178,10 +2365,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2189,10 +2376,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2200,10 +2387,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2211,10 +2398,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2222,10 +2409,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2233,10 +2420,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2244,10 +2431,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2255,10 +2442,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2266,10 +2453,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2277,10 +2464,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2288,10 +2475,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2299,10 +2486,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2310,10 +2497,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2321,10 +2508,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2332,10 +2519,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2343,10 +2530,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2354,10 +2541,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2365,10 +2552,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2376,10 +2563,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2387,10 +2574,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2398,10 +2585,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2409,10 +2596,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2420,10 +2607,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2431,10 +2618,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2442,10 +2629,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2453,10 +2640,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2464,10 +2651,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2475,10 +2662,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2486,10 +2673,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2497,10 +2684,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2508,10 +2695,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2519,10 +2706,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2530,10 +2717,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2541,10 +2728,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2552,10 +2739,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2563,10 +2750,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2574,10 +2761,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2585,10 +2772,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2596,10 +2783,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2607,10 +2794,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2618,10 +2805,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2629,10 +2816,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2640,10 +2827,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2651,10 +2838,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2662,10 +2849,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2673,10 +2860,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2684,10 +2871,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2695,10 +2882,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2706,10 +2893,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2717,10 +2904,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2728,10 +2915,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2739,10 +2926,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2750,10 +2937,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2761,10 +2948,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2772,10 +2959,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2783,10 +2970,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2794,10 +2981,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2805,10 +2992,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2816,10 +3003,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2827,10 +3014,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2838,10 +3025,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2849,10 +3036,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2860,10 +3047,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2871,10 +3058,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2882,10 +3069,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2893,10 +3080,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2904,10 +3091,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2915,10 +3102,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2926,10 +3113,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2937,10 +3124,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2948,10 +3135,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2959,10 +3146,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2970,10 +3157,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2981,10 +3168,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2992,10 +3179,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3003,10 +3190,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3014,10 +3201,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3025,10 +3212,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="115">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -353,16 +353,10 @@
     <t xml:space="preserve">styl_odpowiedzi_tekstowej</t>
   </si>
   <si>
-    <t xml:space="preserve">2_prompt_obrazek_styl.txt</t>
+    <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_Quadriptych.txt</t>
   </si>
   <si>
     <t xml:space="preserve">requiem_styl_Odpowiedzi_tekstowej_1_7.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_Quadriptych.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">styl_kosmiczny.txt</t>
   </si>
   <si>
     <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_system.txt</t>
@@ -510,7 +504,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -547,24 +541,20 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -828,8 +818,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1839,7 +1829,7 @@
       <c r="B1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="11" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1881,7 +1871,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>111</v>
@@ -1892,7 +1882,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>111</v>
@@ -1903,7 +1893,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>111</v>
@@ -1914,7 +1904,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>111</v>
@@ -1925,21 +1915,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>113</v>
+      <c r="B10" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1947,21 +1937,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>113</v>
+      <c r="B12" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1969,21 +1959,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>113</v>
+      <c r="B14" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1991,21 +1981,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>113</v>
+      <c r="B16" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2013,21 +2003,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>113</v>
+      <c r="B18" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2035,21 +2025,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>113</v>
+      <c r="B20" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2057,21 +2047,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>113</v>
+      <c r="B22" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2079,21 +2069,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2101,21 +2091,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2123,21 +2113,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2145,21 +2135,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2167,21 +2157,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2189,21 +2179,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2211,21 +2201,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2233,21 +2223,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2255,21 +2245,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2277,21 +2267,21 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2299,21 +2289,21 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>113</v>
+      <c r="B44" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2321,21 +2311,21 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>113</v>
+      <c r="B46" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2343,21 +2333,21 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>113</v>
+      <c r="B48" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2365,21 +2355,21 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>113</v>
+      <c r="B50" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2387,10 +2377,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2398,10 +2388,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2409,10 +2399,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2420,10 +2410,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2431,10 +2421,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2442,10 +2432,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2453,10 +2443,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2464,10 +2454,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2475,10 +2465,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2486,10 +2476,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2497,10 +2487,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2508,10 +2498,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2519,10 +2509,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2530,10 +2520,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2541,10 +2531,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2552,10 +2542,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2563,10 +2553,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2574,10 +2564,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2585,10 +2575,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2596,10 +2586,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2607,10 +2597,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2618,10 +2608,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2629,10 +2619,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2640,10 +2630,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2651,10 +2641,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2662,10 +2652,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2673,10 +2663,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2684,10 +2674,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2695,10 +2685,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2706,10 +2696,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2717,10 +2707,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2728,10 +2718,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2739,10 +2729,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2750,10 +2740,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2761,10 +2751,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2772,10 +2762,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2783,10 +2773,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2794,10 +2784,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2805,10 +2795,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2816,10 +2806,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2827,10 +2817,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2838,10 +2828,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2849,10 +2839,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2860,10 +2850,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2871,10 +2861,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2882,10 +2872,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2893,10 +2883,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2904,10 +2894,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2915,10 +2905,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2926,10 +2916,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2937,10 +2927,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2948,10 +2938,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2959,10 +2949,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2970,10 +2960,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2981,10 +2971,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2992,10 +2982,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3003,10 +2993,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3014,10 +3004,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3025,10 +3015,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3036,10 +3026,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3047,10 +3037,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3058,10 +3048,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3069,10 +3059,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3080,10 +3070,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3091,10 +3081,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3102,10 +3092,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3113,10 +3103,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3124,10 +3114,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3135,10 +3125,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3146,10 +3136,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3157,10 +3147,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3168,10 +3158,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3179,10 +3169,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3190,10 +3180,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3201,10 +3191,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3212,10 +3202,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="114">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -359,13 +359,10 @@
     <t xml:space="preserve">requiem_styl_Odpowiedzi_tekstowej_1_7.txt</t>
   </si>
   <si>
-    <t xml:space="preserve">requiem_WYSLANNIK_flux_groq_system.txt</t>
+    <t xml:space="preserve">requiem_WYSLANNIK_system_8_.txt</t>
   </si>
   <si>
     <t xml:space="preserve">requiem_budowlaniec_drzwi.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">requiem_WYSLANNIK_system_8_.txt</t>
   </si>
 </sst>
 </file>
@@ -1907,7 +1904,7 @@
         <v>110</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2072,7 +2069,7 @@
         <v>110</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2292,7 +2289,7 @@
         <v>110</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2303,7 +2300,7 @@
         <v>110</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2314,7 +2311,7 @@
         <v>110</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2325,7 +2322,7 @@
         <v>110</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2336,7 +2333,7 @@
         <v>110</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2347,7 +2344,7 @@
         <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2358,7 +2355,7 @@
         <v>110</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2369,7 +2366,7 @@
         <v>110</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2380,7 +2377,7 @@
         <v>110</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2391,7 +2388,7 @@
         <v>110</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2402,7 +2399,7 @@
         <v>110</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2413,7 +2410,7 @@
         <v>110</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2424,7 +2421,7 @@
         <v>110</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2435,7 +2432,7 @@
         <v>110</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2446,7 +2443,7 @@
         <v>110</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2457,7 +2454,7 @@
         <v>110</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2468,7 +2465,7 @@
         <v>110</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2479,7 +2476,7 @@
         <v>110</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2490,7 +2487,7 @@
         <v>110</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2501,7 +2498,7 @@
         <v>110</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2512,7 +2509,7 @@
         <v>110</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2523,7 +2520,7 @@
         <v>110</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2534,7 +2531,7 @@
         <v>110</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2545,7 +2542,7 @@
         <v>110</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2556,7 +2553,7 @@
         <v>110</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2567,7 +2564,7 @@
         <v>110</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2578,7 +2575,7 @@
         <v>110</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2589,7 +2586,7 @@
         <v>110</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2600,7 +2597,7 @@
         <v>110</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2611,7 +2608,7 @@
         <v>110</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2622,7 +2619,7 @@
         <v>110</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2633,7 +2630,7 @@
         <v>110</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2644,7 +2641,7 @@
         <v>110</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2655,7 +2652,7 @@
         <v>110</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2666,7 +2663,7 @@
         <v>110</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2677,7 +2674,7 @@
         <v>110</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2688,7 +2685,7 @@
         <v>110</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2699,7 +2696,7 @@
         <v>110</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2710,7 +2707,7 @@
         <v>110</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2721,7 +2718,7 @@
         <v>110</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2732,7 +2729,7 @@
         <v>110</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2743,7 +2740,7 @@
         <v>110</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2754,7 +2751,7 @@
         <v>110</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2765,7 +2762,7 @@
         <v>110</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2776,7 +2773,7 @@
         <v>110</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2787,7 +2784,7 @@
         <v>110</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2798,7 +2795,7 @@
         <v>110</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2809,7 +2806,7 @@
         <v>110</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2820,7 +2817,7 @@
         <v>110</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2831,7 +2828,7 @@
         <v>110</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2842,7 +2839,7 @@
         <v>110</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2853,7 +2850,7 @@
         <v>110</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2864,7 +2861,7 @@
         <v>110</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2875,7 +2872,7 @@
         <v>110</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2886,7 +2883,7 @@
         <v>110</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2897,7 +2894,7 @@
         <v>110</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2908,7 +2905,7 @@
         <v>110</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2919,7 +2916,7 @@
         <v>110</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2930,7 +2927,7 @@
         <v>110</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2941,7 +2938,7 @@
         <v>110</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2952,7 +2949,7 @@
         <v>110</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2963,7 +2960,7 @@
         <v>110</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2974,7 +2971,7 @@
         <v>110</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2985,7 +2982,7 @@
         <v>110</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2996,7 +2993,7 @@
         <v>110</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3007,7 +3004,7 @@
         <v>110</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3018,7 +3015,7 @@
         <v>110</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3029,7 +3026,7 @@
         <v>110</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3040,7 +3037,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3051,7 +3048,7 @@
         <v>110</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3062,7 +3059,7 @@
         <v>110</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3073,7 +3070,7 @@
         <v>110</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3084,7 +3081,7 @@
         <v>110</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3095,7 +3092,7 @@
         <v>110</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3106,7 +3103,7 @@
         <v>110</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3117,7 +3114,7 @@
         <v>110</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3128,7 +3125,7 @@
         <v>110</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3139,7 +3136,7 @@
         <v>110</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3150,7 +3147,7 @@
         <v>110</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3161,7 +3158,7 @@
         <v>110</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3172,7 +3169,7 @@
         <v>110</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3183,7 +3180,7 @@
         <v>110</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3194,7 +3191,7 @@
         <v>110</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3205,7 +3202,7 @@
         <v>110</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -856,7 +856,7 @@
         <v>90</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -876,7 +876,7 @@
         <v>90</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>12</v>
@@ -905,10 +905,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H4" s="10" t="n">
         <v>0</v>
@@ -937,10 +937,10 @@
         <v>24</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>25</v>
@@ -969,10 +969,10 @@
         <v>31</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>32</v>
@@ -1004,7 +1004,7 @@
         <v>90</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>39</v>
@@ -1036,7 +1036,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>46</v>
@@ -1064,7 +1064,7 @@
         <v>90</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>51</v>
@@ -1092,7 +1092,7 @@
         <v>90</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1108,7 +1108,7 @@
         <v>90</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1124,7 +1124,7 @@
         <v>90</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1140,7 +1140,7 @@
         <v>90</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1156,7 +1156,7 @@
         <v>90</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1172,7 +1172,7 @@
         <v>90</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1188,7 +1188,7 @@
         <v>90</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1204,7 +1204,7 @@
         <v>90</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1220,7 +1220,7 @@
         <v>90</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1236,7 +1236,7 @@
         <v>90</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1251,7 +1251,7 @@
         <v>90</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1266,7 +1266,7 @@
         <v>90</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1281,7 +1281,7 @@
         <v>90</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1301,7 +1301,7 @@
         <v>90</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="71.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1318,7 +1318,7 @@
         <v>90</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1335,10 +1335,10 @@
         <v>70</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1358,7 +1358,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1378,7 +1378,7 @@
         <v>90</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1398,7 +1398,7 @@
         <v>90</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1416,7 +1416,7 @@
         <v>90</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1434,7 +1434,7 @@
         <v>90</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1452,7 +1452,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1470,7 +1470,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1488,7 +1488,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1506,7 +1506,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1524,7 +1524,7 @@
         <v>90</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1542,7 +1542,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1560,7 +1560,7 @@
         <v>90</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1578,7 +1578,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1596,7 +1596,7 @@
         <v>90</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1614,7 +1614,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1632,7 +1632,7 @@
         <v>90</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1650,7 +1650,7 @@
         <v>90</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1665,7 +1665,7 @@
         <v>90</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1680,7 +1680,7 @@
         <v>90</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1696,7 +1696,7 @@
         <v>90</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1712,7 +1712,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1728,7 +1728,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1744,7 +1744,7 @@
         <v>90</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1760,7 +1760,7 @@
         <v>90</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1776,7 +1776,7 @@
         <v>90</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1792,7 +1792,7 @@
         <v>90</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2080,7 +2080,7 @@
         <v>110</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2091,7 +2091,7 @@
         <v>110</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2102,7 +2102,7 @@
         <v>110</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2113,7 +2113,7 @@
         <v>110</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2124,7 +2124,7 @@
         <v>110</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2135,7 +2135,7 @@
         <v>110</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="114">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -284,6 +284,9 @@
     <t xml:space="preserve">Remonty - wymiana żarówek w gwiazdach</t>
   </si>
   <si>
+    <t xml:space="preserve">drzwi10.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">Remonty - renowacja planet kamiennych</t>
   </si>
   <si>
@@ -303,9 +306,6 @@
   </si>
   <si>
     <t xml:space="preserve">Remonty - instalacja klimatyzacji w Piekle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drzwi10.png</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - remont tunelu czasoprzestrzennego</t>
@@ -1481,7 +1481,7 @@
         <v>86</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7" t="n">
@@ -1496,11 +1496,9 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>73</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C34" s="0"/>
       <c r="D34" s="6"/>
       <c r="E34" s="7" t="n">
         <v>90</v>
@@ -1514,11 +1512,9 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C35" s="6"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7" t="n">
         <v>90</v>
@@ -1532,11 +1528,9 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>79</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C36" s="7"/>
       <c r="D36" s="6"/>
       <c r="E36" s="7" t="n">
         <v>90</v>
@@ -1550,11 +1544,9 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>81</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C37" s="0"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7" t="n">
         <v>90</v>
@@ -1568,11 +1560,9 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>83</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C38" s="0"/>
       <c r="D38" s="6"/>
       <c r="E38" s="7" t="n">
         <v>90</v>
@@ -1586,11 +1576,9 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>85</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C39" s="0"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7" t="n">
         <v>90</v>
@@ -1604,11 +1592,9 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="6" t="s">
         <v>94</v>
       </c>
+      <c r="C40" s="0"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7" t="n">
         <v>90</v>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="etapy" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="113">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -360,9 +360,6 @@
   </si>
   <si>
     <t xml:space="preserve">requiem_WYSLANNIK_system_8_.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">requiem_budowlaniec_drzwi.txt</t>
   </si>
 </sst>
 </file>
@@ -1498,7 +1495,6 @@
       <c r="B34" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="0"/>
       <c r="D34" s="6"/>
       <c r="E34" s="7" t="n">
         <v>90</v>
@@ -1546,7 +1542,6 @@
       <c r="B37" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C37" s="0"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7" t="n">
         <v>90</v>
@@ -1562,7 +1557,6 @@
       <c r="B38" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="0"/>
       <c r="D38" s="6"/>
       <c r="E38" s="7" t="n">
         <v>90</v>
@@ -1578,7 +1572,6 @@
       <c r="B39" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C39" s="0"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7" t="n">
         <v>90</v>
@@ -1594,7 +1587,6 @@
       <c r="B40" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="0"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7" t="n">
         <v>90</v>
@@ -2132,7 +2124,7 @@
         <v>110</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2143,7 +2135,7 @@
         <v>110</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2154,7 +2146,7 @@
         <v>110</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2165,7 +2157,7 @@
         <v>110</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2176,7 +2168,7 @@
         <v>110</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2187,7 +2179,7 @@
         <v>110</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2198,7 +2190,7 @@
         <v>110</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2209,7 +2201,7 @@
         <v>110</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2220,7 +2212,7 @@
         <v>110</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2231,7 +2223,7 @@
         <v>110</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2242,7 +2234,7 @@
         <v>110</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2253,7 +2245,7 @@
         <v>110</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2264,7 +2256,7 @@
         <v>110</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -853,7 +853,7 @@
         <v>90</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -873,7 +873,7 @@
         <v>90</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>12</v>
@@ -905,7 +905,7 @@
         <v>90</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4" s="10" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>90</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>25</v>
@@ -969,7 +969,7 @@
         <v>90</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>32</v>
@@ -1001,7 +1001,7 @@
         <v>90</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>39</v>
@@ -1033,7 +1033,7 @@
         <v>90</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>46</v>
@@ -1061,7 +1061,7 @@
         <v>90</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>51</v>
@@ -1089,7 +1089,7 @@
         <v>90</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1105,7 +1105,7 @@
         <v>90</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1121,7 +1121,7 @@
         <v>90</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1137,7 +1137,7 @@
         <v>90</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1153,7 +1153,7 @@
         <v>90</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1169,7 +1169,7 @@
         <v>90</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1185,7 +1185,7 @@
         <v>90</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1201,7 +1201,7 @@
         <v>90</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1217,7 +1217,7 @@
         <v>90</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1233,7 +1233,7 @@
         <v>90</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1248,7 +1248,7 @@
         <v>90</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1263,7 +1263,7 @@
         <v>90</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1278,7 +1278,7 @@
         <v>90</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1296,7 +1296,7 @@
         <v>90</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="71.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1311,7 +1311,7 @@
         <v>90</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1329,7 +1329,7 @@
         <v>90</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1347,7 +1347,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1365,7 +1365,7 @@
         <v>90</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1383,7 +1383,7 @@
         <v>90</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1401,7 +1401,7 @@
         <v>90</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1419,7 +1419,7 @@
         <v>90</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1437,7 +1437,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1455,7 +1455,7 @@
         <v>90</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1475,7 +1475,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1490,7 +1490,7 @@
         <v>90</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1506,7 +1506,7 @@
         <v>90</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1522,7 +1522,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1537,7 +1537,7 @@
         <v>90</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1552,7 +1552,7 @@
         <v>90</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1567,7 +1567,7 @@
         <v>90</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1582,7 +1582,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1600,7 +1600,7 @@
         <v>90</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1618,7 +1618,7 @@
         <v>90</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1633,7 +1633,7 @@
         <v>90</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1648,7 +1648,7 @@
         <v>90</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1664,7 +1664,7 @@
         <v>90</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1680,7 +1680,7 @@
         <v>90</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1696,7 +1696,7 @@
         <v>90</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1712,7 +1712,7 @@
         <v>90</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1728,7 +1728,7 @@
         <v>90</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1744,7 +1744,7 @@
         <v>90</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1760,7 +1760,7 @@
         <v>90</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/prompts/requiem_etapy.xlsx
+++ b/prompts/requiem_etapy.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="112">
   <si>
     <t xml:space="preserve">etap</t>
   </si>
@@ -282,9 +282,6 @@
   </si>
   <si>
     <t xml:space="preserve">drzwi10.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calosc.mp4</t>
   </si>
   <si>
     <t xml:space="preserve">Remonty - renowacja planet kamiennych</t>
@@ -1468,9 +1465,7 @@
       <c r="C33" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>87</v>
-      </c>
+      <c r="D33" s="7"/>
       <c r="E33" s="7" t="n">
         <v>90</v>
       </c>
@@ -1483,7 +1478,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="7" t="n">
@@ -1498,7 +1493,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="7"/>
@@ -1514,7 +1509,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="6"/>
@@ -1530,7 +1525,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7" t="n">
@@ -1545,7 +1540,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="7" t="n">
@@ -1560,7 +1555,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="7" t="n">
@@ -1575,7 +1570,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="7" t="n">
@@ -1590,10 +1585,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="7" t="n">
@@ -1608,10 +1603,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="7" t="n">
@@ -1626,7 +1621,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7" t="n">
@@ -1641,7 +1636,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="7" t="n">
@@ -1656,7 +1651,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -1672,7 +1667,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="6"/>
@@ -1688,7 +1683,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
@@ -1704,7 +1699,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
@@ -1720,7 +1715,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -1736,7 +1731,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
@@ -1752,7 +1747,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -1792,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1803,10 +1798,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1814,10 +1809,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1825,10 +1820,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1836,10 +1831,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1847,10 +1842,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1858,10 +1853,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1869,10 +1864,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1880,10 +1875,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1891,10 +1886,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1902,10 +1897,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1913,10 +1908,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1924,10 +1919,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1935,10 +1930,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1946,10 +1941,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1957,10 +1952,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1968,10 +1963,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1979,10 +1974,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1990,10 +1985,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2001,10 +1996,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2012,10 +2007,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2023,10 +2018,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2034,10 +2029,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2045,10 +2040,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2056,10 +2051,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2067,10 +2062,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2078,10 +2073,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2089,10 +2084,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2100,10 +2095,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2111,10 +2106,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2122,10 +2117,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2133,10 +2128,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2144,10 +2139,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2155,10 +2150,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2166,10 +2161,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2177,10 +2172,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2188,10 +2183,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2199,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2210,10 +2205,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2221,10 +2216,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2232,10 +2227,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2243,10 +2238,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2254,10 +2249,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2265,10 +2260,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2276,10 +2271,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2287,10 +2282,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2298,10 +2293,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2309,10 +2304,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2320,10 +2315,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2331,10 +2326,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2342,10 +2337,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2353,10 +2348,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2364,10 +2359,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2375,10 +2370,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2386,10 +2381,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2397,10 +2392,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2408,10 +2403,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2419,10 +2414,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2430,10 +2425,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2441,10 +2436,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2452,10 +2447,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2463,10 +2458,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2474,10 +2469,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2485,10 +2480,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2496,10 +2491,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2507,10 +2502,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2518,10 +2513,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2529,10 +2524,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2540,10 +2535,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2551,10 +2546,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2562,10 +2557,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2573,10 +2568,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2584,10 +2579,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2595,10 +2590,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2606,10 +2601,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2617,10 +2612,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2628,10 +2623,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2639,10 +2634,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2650,10 +2645,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2661,10 +2656,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2672,10 +2667,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2683,10 +2678,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2694,10 +2689,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2705,10 +2700,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2716,10 +2711,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2727,10 +2722,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2738,10 +2733,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2749,10 +2744,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2760,10 +2755,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2771,10 +2766,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2782,10 +2777,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2793,10 +2788,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2804,10 +2799,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2815,10 +2810,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2826,10 +2821,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2837,10 +2832,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2848,10 +2843,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2859,10 +2854,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2870,10 +2865,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2881,10 +2876,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2892,10 +2887,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2903,10 +2898,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2914,10 +2909,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2925,10 +2920,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2936,10 +2931,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2947,10 +2942,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2958,10 +2953,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2969,10 +2964,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2980,10 +2975,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2991,10 +2986,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3002,10 +2997,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3013,10 +3008,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3024,10 +3019,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3035,10 +3030,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3046,10 +3041,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3057,10 +3052,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3068,10 +3063,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3079,10 +3074,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3090,10 +3085,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3101,10 +3096,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3112,10 +3107,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3123,10 +3118,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3134,10 +3129,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3145,10 +3140,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3156,10 +3151,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3167,10 +3162,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
